--- a/Testing Tasks/StaffSync_EmployeeMaster_Testing_Tasks_Complete_Dashboard.xlsx
+++ b/Testing Tasks/StaffSync_EmployeeMaster_Testing_Tasks_Complete_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\StaffSync\Testing Tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA03485-4048-44F2-8132-CE9E299AC808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43412659-2CB0-411F-A98A-4B75A6F6610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="191">
   <si>
     <t>Result Summary (Update counts manually or with formulas later)</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Screen loads without errors</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>EMD-002</t>
   </si>
   <si>
@@ -171,12 +168,6 @@
     <t>EMD-005</t>
   </si>
   <si>
-    <t>Save new employee</t>
-  </si>
-  <si>
-    <t>Employee saved successfully</t>
-  </si>
-  <si>
     <t>EMD-006</t>
   </si>
   <si>
@@ -609,16 +600,10 @@
     <t>Employee deleted correctly</t>
   </si>
   <si>
-    <t>EMD-054</t>
-  </si>
-  <si>
     <t>Audit log validation</t>
   </si>
   <si>
     <t>Audit log updated</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Not Applicable</t>
@@ -755,13 +740,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1104,16 +1089,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1264,13 +1249,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1810,10 +1795,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="30" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1849,12 +1837,9 @@
       <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" t="str">
         <f t="shared" ref="E2:E33" si="0">IF(D2="Yes","Pass",IF(D2="No","Fail",IF(D2="Not Applicable","Pass",IF(D2="Blocked","Blocked",IF(D2="Pending","Not Executed","")))))</f>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -1862,20 +1847,17 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>194</v>
-      </c>
       <c r="E3" t="str">
         <f t="shared" si="0"/>
-        <v>Fail</v>
+        <v/>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -1883,20 +1865,17 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>195</v>
-      </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -1904,20 +1883,17 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1925,7 +1901,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -1933,12 +1909,9 @@
       <c r="C6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1946,7 +1919,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -1954,12 +1927,9 @@
       <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -1967,7 +1937,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -1975,12 +1945,9 @@
       <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
-        <v>194</v>
-      </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v>Fail</v>
+        <v/>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -1988,7 +1955,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
@@ -1996,12 +1963,9 @@
       <c r="C9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
-        <v>195</v>
-      </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
-        <v>Pass</v>
+        <v/>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -2009,7 +1973,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -2027,7 +1991,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
         <v>60</v>
@@ -2045,7 +2009,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
@@ -2063,7 +2027,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>66</v>
@@ -2081,7 +2045,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>69</v>
@@ -2099,7 +2063,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
@@ -2117,7 +2081,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
@@ -2135,7 +2099,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
         <v>78</v>
@@ -2153,7 +2117,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -2171,7 +2135,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>84</v>
@@ -2189,7 +2153,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
         <v>87</v>
@@ -2207,7 +2171,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
@@ -2225,7 +2189,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>93</v>
@@ -2243,7 +2207,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>96</v>
@@ -2261,7 +2225,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
         <v>99</v>
@@ -2279,7 +2243,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
         <v>102</v>
@@ -2297,7 +2261,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>105</v>
@@ -2315,7 +2279,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>108</v>
@@ -2333,7 +2297,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>111</v>
@@ -2351,7 +2315,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>114</v>
@@ -2369,7 +2333,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>117</v>
@@ -2387,7 +2351,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
         <v>120</v>
@@ -2405,7 +2369,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
         <v>123</v>
@@ -2423,7 +2387,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
         <v>126</v>
@@ -2441,7 +2405,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
         <v>129</v>
@@ -2450,7 +2414,7 @@
         <v>130</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" ref="E34:E65" si="1">IF(D34="Yes","Pass",IF(D34="No","Fail",IF(D34="Not Applicable","Pass",IF(D34="Blocked","Blocked",IF(D34="Pending","Not Executed","")))))</f>
+        <f t="shared" ref="E34:E54" si="1">IF(D34="Yes","Pass",IF(D34="No","Fail",IF(D34="Not Applicable","Pass",IF(D34="Blocked","Blocked",IF(D34="Pending","Not Executed","")))))</f>
         <v/>
       </c>
       <c r="G34" t="s">
@@ -2459,7 +2423,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
         <v>132</v>
@@ -2477,7 +2441,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
         <v>135</v>
@@ -2495,7 +2459,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -2513,7 +2477,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
         <v>141</v>
@@ -2531,7 +2495,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>144</v>
@@ -2549,7 +2513,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
         <v>147</v>
@@ -2567,7 +2531,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>150</v>
@@ -2585,7 +2549,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>153</v>
@@ -2603,7 +2567,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>156</v>
@@ -2621,7 +2585,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>159</v>
@@ -2639,7 +2603,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>162</v>
@@ -2657,7 +2621,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
         <v>165</v>
@@ -2675,7 +2639,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>168</v>
@@ -2693,7 +2657,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>171</v>
@@ -2711,7 +2675,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>174</v>
@@ -2729,7 +2693,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>177</v>
@@ -2747,7 +2711,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
         <v>180</v>
@@ -2765,7 +2729,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>183</v>
@@ -2783,7 +2747,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
         <v>186</v>
@@ -2801,13 +2765,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" t="s">
         <v>188</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>189</v>
-      </c>
-      <c r="C54" t="s">
-        <v>190</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="1"/>
@@ -2817,30 +2781,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>191</v>
-      </c>
-      <c r="B55" t="s">
-        <v>192</v>
-      </c>
-      <c r="C55" t="s">
-        <v>193</v>
-      </c>
-      <c r="E55" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G55" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="D2:D55" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D2:D54" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D55" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="D2:D54" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No,Not Applicable,Blocked,Pending"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2881,7 +2827,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF('Employee Master Tasks'!E:E,"Pass")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2890,16 +2836,16 @@
       </c>
       <c r="B5">
         <f>COUNTIF('Employee Master Tasks'!E:E,"Fail")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B6">
         <f>COUNTIF('Employee Master Tasks'!D:D,"Not Applicable")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2908,7 +2854,7 @@
       </c>
       <c r="B7">
         <f>COUNTA('Employee Master Tasks'!A:A)-1-B4-B5-B6</f>
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2931,7 +2877,7 @@
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I10" t="s">
         <v>9</v>
@@ -2953,11 +2899,11 @@
       </c>
       <c r="F11">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D11,'Employee Master Tasks'!E:E,"Pass")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D11,'Employee Master Tasks'!E:E,"Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D11,'Employee Master Tasks'!E:E,"Blocked")</f>
@@ -2965,7 +2911,7 @@
       </c>
       <c r="I11">
         <f t="shared" ref="I11:I25" si="0">E11-F11-G11-H11</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2984,7 +2930,7 @@
       </c>
       <c r="F12">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D12,'Employee Master Tasks'!E:E,"Pass")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D12,'Employee Master Tasks'!E:E,"Fail")</f>
@@ -2996,7 +2942,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -3015,11 +2961,11 @@
       </c>
       <c r="F13">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D13,'Employee Master Tasks'!E:E,"Pass")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D13,'Employee Master Tasks'!E:E,"Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D13,'Employee Master Tasks'!E:E,"Blocked")</f>
@@ -3027,7 +2973,7 @@
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -3383,7 +3329,7 @@
       </c>
       <c r="E25">
         <f>COUNTIF('Employee Master Tasks'!G:G,D25)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <f>COUNTIFS('Employee Master Tasks'!G:G,D25,'Employee Master Tasks'!E:E,"Pass")</f>
@@ -3399,7 +3345,7 @@
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
